--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_14.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_14.xlsx
@@ -471,98 +471,98 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>42858</v>
+        <v>20609</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anthony Castro</t>
+          <t>Bárbara da Cunha</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atendimento ao Cliente</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45102</v>
+        <v>45094</v>
       </c>
       <c r="G2" t="n">
-        <v>6156.61</v>
+        <v>11810.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7108</v>
+        <v>35911</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luiz Otávio Silveira</t>
+          <t>Sarah Almeida</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45102</v>
+        <v>45100</v>
       </c>
       <c r="G3" t="n">
-        <v>7938.3</v>
+        <v>7915.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>27514</v>
+        <v>69786</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Luigi Cunha</t>
+          <t>Levi da Rosa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Consulta médica</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45092</v>
+        <v>45085</v>
       </c>
       <c r="G4" t="n">
-        <v>11828.89</v>
+        <v>12445.87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51805</v>
+        <v>16498</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kaique Azevedo</t>
+          <t>Enzo Gabriel Moreira</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,191 +572,191 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45099</v>
+        <v>45083</v>
       </c>
       <c r="G5" t="n">
-        <v>8917.27</v>
+        <v>11385.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50734</v>
+        <v>78858</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stella Nogueira</t>
+          <t>Lucas da Costa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45087</v>
+        <v>45082</v>
       </c>
       <c r="G6" t="n">
-        <v>3880.59</v>
+        <v>12419.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>31498</v>
+        <v>87880</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lucas Nunes</t>
+          <t>Luiz Miguel Dias</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>45104</v>
       </c>
       <c r="G7" t="n">
-        <v>2736.26</v>
+        <v>4803.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5975</v>
+        <v>80817</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gabrielly Barros</t>
+          <t>Antônio Oliveira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45094</v>
+        <v>45090</v>
       </c>
       <c r="G8" t="n">
-        <v>7203.93</v>
+        <v>8751.879999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30219</v>
+        <v>55900</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Theo Moraes</t>
+          <t>Maria Clara Rocha</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45098</v>
+        <v>45078</v>
       </c>
       <c r="G9" t="n">
-        <v>3750.1</v>
+        <v>10208.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41530</v>
+        <v>83121</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Juliana Ramos</t>
+          <t>Dr. Pedro Henrique Campos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45089</v>
+        <v>45104</v>
       </c>
       <c r="G10" t="n">
-        <v>4756.81</v>
+        <v>5964.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81939</v>
+        <v>71033</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sr. Luiz Felipe Almeida</t>
+          <t>Dr. Danilo Novaes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>45102</v>
       </c>
       <c r="G11" t="n">
-        <v>5926.82</v>
+        <v>4385.33</v>
       </c>
     </row>
   </sheetData>
